--- a/artfynd/A 5119-2023 artfynd.xlsx
+++ b/artfynd/A 5119-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5119-2023 artfynd.xlsx
+++ b/artfynd/A 5119-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1024,6 +1024,126 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123355863</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57497</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sandstorps mosse, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>533084</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6442390</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tjärstad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Turid Seidlitz</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Turid Seidlitz</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5119-2023 artfynd.xlsx
+++ b/artfynd/A 5119-2023 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>123355863</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>57500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 5119-2023 artfynd.xlsx
+++ b/artfynd/A 5119-2023 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>123355863</v>
       </c>
       <c r="B5" t="n">
-        <v>57500</v>
+        <v>57506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 5119-2023 artfynd.xlsx
+++ b/artfynd/A 5119-2023 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>123355863</v>
       </c>
       <c r="B5" t="n">
-        <v>57506</v>
+        <v>57509</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 5119-2023 artfynd.xlsx
+++ b/artfynd/A 5119-2023 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>123355863</v>
       </c>
       <c r="B5" t="n">
-        <v>57509</v>
+        <v>57510</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 5119-2023 artfynd.xlsx
+++ b/artfynd/A 5119-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1144,6 +1144,128 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132447120</v>
+      </c>
+      <c r="B6" t="n">
+        <v>9406</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>101246</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ekoxe</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>S om Södra Gryten, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>533225</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6442514</v>
+      </c>
+      <c r="S6" t="n">
+        <v>75</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tjärstad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flög intill kvarlämnad högstubbe på hygget</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erik Widén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erik Widén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5119-2023 artfynd.xlsx
+++ b/artfynd/A 5119-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>78599010</v>
+        <v>17251234</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>105117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1560</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ödetorpet Lindstugan., Ög</t>
+          <t>Sandstorp, 500 m NO, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533306.2934898434</v>
+        <v>533188</v>
       </c>
       <c r="R2" t="n">
-        <v>6442478.589014518</v>
+        <v>6442416</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-05-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-05-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-12-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre uppgifter om Östergötlands flora. Referens: Andersson, Janne 2000. Brev till Folke Lind 9 jan 2000. Brev och Lista i PÖF Arkiv, Norrköping, 14 s. Inlagda i Artportalen av Tommy Tyrberg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,55 +767,46 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Skogsglänta vid torpgrund</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Tommy Tyrberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson</t>
+          <t>Via Tommy Tyrberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>78599000</v>
+        <v>78497332</v>
       </c>
       <c r="B3" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>105117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>1560</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Spindelört</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Thesium alpinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,20 +814,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ödetorpet Lindstugan., Ög</t>
+          <t>Sandstorp, 500 m NO, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533306.2934898434</v>
+        <v>533193</v>
       </c>
       <c r="R3" t="n">
-        <v>6442478.589014518</v>
+        <v>6442414</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-05-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-05-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,71 +879,75 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Skogsglänta vid torpgrund</t>
+          <t>torrängsartad grusvägkant</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>78599008</v>
+        <v>132447120</v>
       </c>
       <c r="B4" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>9414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>101246</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ödetorpet Lindstugan., Ög</t>
+          <t>S om Södra Gryten, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533306.2934898434</v>
+        <v>533225</v>
       </c>
       <c r="R4" t="n">
-        <v>6442478.589014518</v>
+        <v>6442514</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +971,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-05-24</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-05-24</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flög intill kvarlämnad högstubbe på hygget</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,23 +1000,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Skogsglänta vid torpgrund</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Erik Widén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo, Åke Svensson</t>
+          <t>Erik Widén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1029,12 +1022,7 @@
         <v>123355863</v>
       </c>
       <c r="B5" t="n">
-        <v>57510</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,57 +1134,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132447120</v>
+        <v>78599008</v>
       </c>
       <c r="B6" t="n">
-        <v>9406</v>
+        <v>110078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101246</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>S om Södra Gryten, Ög</t>
+          <t>Ödetorpet Lindstugan., Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533225</v>
+        <v>533306</v>
       </c>
       <c r="R6" t="n">
-        <v>6442514</v>
+        <v>6442479</v>
       </c>
       <c r="S6" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,27 +1199,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>22:30</t>
+          <t>2019-05-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flög intill kvarlämnad högstubbe på hygget</t>
+          <t>2019-05-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,22 +1213,332 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Skogsglänta vid torpgrund</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Widén</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Widén</t>
+          <t>Charlotte Wigermo, Åke Svensson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>78599000</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ödetorpet Lindstugan., Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>533306</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6442479</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tjärstad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-05-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-05-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Skogsglänta vid torpgrund</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>78599012</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sandstorp, 500 m NO., Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>533193</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6442414</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tjärstad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-05-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-05-24</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Sandig vägkant</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>78599010</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ödetorpet Lindstugan., Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>533306</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6442479</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tjärstad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2019-05-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2019-05-24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Skogsglänta vid torpgrund</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5119-2023 artfynd.xlsx
+++ b/artfynd/A 5119-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17251234</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78497332</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132447120</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123355863</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,6 +1258,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78599008</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1335,6 +1365,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78599000</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1437,6 +1472,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78599012</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1539,8 +1579,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78599010</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>